--- a/DATA/ARCHIVE/random_normal_forecast_data.xlsx
+++ b/DATA/ARCHIVE/random_normal_forecast_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/ARCHIVE/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="111" documentId="8_{4AC4CF64-28C5-4046-81FC-BB8B210E8F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159E750F-3F98-4CCC-947A-24603676EB46}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="9" xr2:uid="{A5115543-AC87-4E62-8A65-1522949D5C3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="9" activeTab="14" xr2:uid="{A5115543-AC87-4E62-8A65-1522949D5C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
